--- a/data/reports/2024-04-15/2024-04-15_duplicates.xlsx
+++ b/data/reports/2024-04-15/2024-04-15_duplicates.xlsx
@@ -141,7 +141,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=949115a61bc13c102eb2a82fe54bcb0c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
+    <t>RMD0005813</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -157,31 +157,31 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>Glenn Dalgliesh</t>
+  </si>
+  <si>
+    <t>VP of Operations</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>'+14439121000</t>
+  </si>
+  <si>
+    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004723</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005813</t>
-  </si>
-  <si>
-    <t>Glenn Dalgliesh</t>
-  </si>
-  <si>
-    <t>VP of Operations</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>'+14439121000</t>
-  </si>
-  <si>
-    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004139</t>
+    <t>RMD0009352</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -197,28 +197,28 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>800-7096314</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004139</t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
     <t>800-709-6314</t>
   </si>
   <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009352</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>800-7096314</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008972</t>
@@ -252,7 +252,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
+    <t>RMD0009020</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -268,6 +268,18 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT Department</t>
+  </si>
+  <si>
+    <t>2089473900</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009019</t>
+  </si>
+  <si>
     <t>IT</t>
   </si>
   <si>
@@ -281,18 +293,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
-  </si>
-  <si>
-    <t>IT Department</t>
-  </si>
-  <si>
-    <t>2089473900</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009084</t>
@@ -380,7 +380,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004389</t>
+    <t>RMD0003929</t>
   </si>
   <si>
     <t>Idealtel Dominicana USA, Inc. dba myidealtel.com</t>
@@ -391,16 +391,16 @@
 Cooper City FL 33328</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004389</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9a075a791b8db4109294113d9c4bcbd5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003929</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005819</t>
+    <t>RMD0004724</t>
   </si>
   <si>
     <t>Ton80 Communications, LLC</t>
@@ -410,19 +410,19 @@
 Anderson SC 29642</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005819</t>
+  </si>
+  <si>
     <t>4109121000</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004724</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004849</t>
+    <t>RMD0004806</t>
   </si>
   <si>
     <t>Smartbiz Telecom, LLC</t>
@@ -433,6 +433,15 @@
 Miami FL 33126</t>
   </si>
   <si>
+    <t>2023-03-24</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004849</t>
+  </si>
+  <si>
     <t>Eduardo Borrero</t>
   </si>
   <si>
@@ -451,29 +460,10 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=beda02fb1bc5f05064c4426de54bcb94&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004806</t>
-  </si>
-  <si>
-    <t>2023-03-24</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005785</t>
+    <t>RMD0005786</t>
   </si>
   <si>
     <t>Edge Fibernet</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005786</t>
   </si>
   <si>
     <t>254 36th Street
@@ -484,10 +474,43 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0003758</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach Florida 33139</t>
+  </si>
+  <si>
+    <t>Davon Person</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Network Operations Center</t>
+  </si>
+  <si>
+    <t>9546248162</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -521,29 +544,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach Florida 33139</t>
-  </si>
-  <si>
-    <t>Davon Person</t>
-  </si>
-  <si>
-    <t>Director of Operations</t>
-  </si>
-  <si>
-    <t>Network Operations Center</t>
-  </si>
-  <si>
-    <t>9546248162</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0002900</t>
   </si>
   <si>
@@ -594,7 +594,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ffdd33cb1bfe781093d3a820f54bcb29&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004110</t>
+    <t>RMD0004738</t>
   </si>
   <si>
     <t>RyTel, LLC</t>
@@ -605,12 +605,6 @@
 Salt Lake City UT 84119</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=64046a611bc1b4102eb2a82fe54bcb32&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004738</t>
-  </si>
-  <si>
     <t>Lamont Snarr</t>
   </si>
   <si>
@@ -628,6 +622,12 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9650dd421bcd38102eb2a82fe54bcb46&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004110</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=64046a611bc1b4102eb2a82fe54bcb32&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005124</t>
@@ -824,7 +824,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=47035e5e1b7eb4109ac2ea04bc4bcbb1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004404</t>
+    <t>RMD0009817</t>
   </si>
   <si>
     <t>Call Bound LLC</t>
@@ -834,25 +834,25 @@
 Miami FL 33131</t>
   </si>
   <si>
+    <t>Sze Dai Wei</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>'+1 305 705-7873</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e2dcbec51bd54510e4ec848ce54bcb81&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004404</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=a73e1eb11b49f41064c4426de54bcb85&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009817</t>
-  </si>
-  <si>
-    <t>Sze Dai Wei</t>
-  </si>
-  <si>
-    <t>Mr.</t>
-  </si>
-  <si>
-    <t>'+1 305 705-7873</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e2dcbec51bd54510e4ec848ce54bcb81&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -862,6 +862,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -880,13 +886,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005461</t>
+    <t>RMD0005569</t>
   </si>
   <si>
     <t>Valstarr Asia</t>
@@ -896,10 +896,25 @@
 Valley Center CA 92082</t>
   </si>
   <si>
+    <t>Vincent W. Kahn</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Systems Admin</t>
+  </si>
+  <si>
+    <t>'+13213288217</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005461</t>
+  </si>
+  <si>
     <t>0031217672</t>
-  </si>
-  <si>
-    <t>Vincent W. Kahn</t>
   </si>
   <si>
     <t>MANAGER</t>
@@ -919,21 +934,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005569</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Systems Admin</t>
-  </si>
-  <si>
-    <t>'+13213288217</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0007936</t>
   </si>
   <si>
@@ -1106,7 +1106,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007939</t>
+    <t>RMD0007944</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1116,28 +1116,28 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>Lance Retter</t>
+  </si>
+  <si>
+    <t>COO</t>
+  </si>
+  <si>
+    <t>7709532500</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007939</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007944</t>
-  </si>
-  <si>
-    <t>Lance Retter</t>
-  </si>
-  <si>
-    <t>COO</t>
-  </si>
-  <si>
-    <t>7709532500</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008064</t>
+    <t>RMD0008097</t>
   </si>
   <si>
     <t>Sam Asher Computing Services, Inc.</t>
@@ -1152,25 +1152,25 @@
 Hyper-Reach</t>
   </si>
   <si>
+    <t>Caitlin Olfano</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>585-643-8708</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4172e7f21b7a3810dcd1ed3be54bcbb5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008064</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=39639b3a1b3a3810dcd1ed3be54bcb5e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008097</t>
-  </si>
-  <si>
-    <t>Caitlin Olfano</t>
-  </si>
-  <si>
-    <t>Manager</t>
-  </si>
-  <si>
-    <t>585-643-8708</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4172e7f21b7a3810dcd1ed3be54bcbb5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008393</t>
+    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T. Inc.</t>
@@ -1178,12 +1178,6 @@
   <si>
     <t>295 Weber St. N
 Ontario N2J 3H8 Waterloo, Canada</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T.</t>
@@ -1201,7 +1195,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=761bc9e71b3eb810d39dddb6bc4bcbe0&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008393</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1211,16 +1211,16 @@
 Greensboro NC 27401</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008610</t>
+    <t>RMD0008612</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1230,6 +1230,21 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008610</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
@@ -1245,28 +1260,19 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008759</t>
+    <t>RMD0008756</t>
   </si>
   <si>
     <t>573 Ocean Blvd
 Hampton NH 03842</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008759</t>
+  </si>
+  <si>
     <t>Jeffrey D Houston</t>
   </si>
   <si>
@@ -1277,12 +1283,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008756</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008755</t>
@@ -5930,14 +5930,28 @@
         <v>45</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -5945,16 +5959,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -5978,28 +5992,14 @@
         <v>45</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6033,9 +6033,15 @@
       <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J7" s="1" t="s">
         <v>57</v>
       </c>
@@ -6093,15 +6099,9 @@
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
         <v>57</v>
       </c>
@@ -6272,31 +6272,27 @@
       <c r="O11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6323,7 +6319,7 @@
         <v>80</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>78</v>
@@ -6332,22 +6328,26 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U12" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>89</v>
       </c>
@@ -6680,28 +6680,14 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>126</v>
-      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="Q19" s="1"/>
       <c r="R19" s="1" t="s">
         <v>26</v>
       </c>
@@ -6709,16 +6695,16 @@
         <v>26</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B20" s="1">
         <v>25462672</v>
@@ -6738,14 +6724,28 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
+      <c r="Q20" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="R20" s="1" t="s">
         <v>26</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>26</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
@@ -6782,47 +6782,33 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U21" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="V21" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B22" s="1">
         <v>26116624</v>
@@ -6842,19 +6828,33 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
+      <c r="Q22" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T22" s="1" t="s">
         <v>34</v>
@@ -6985,40 +6985,34 @@
       <c r="L25" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M25" s="1"/>
+      <c r="N25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="N25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O25" s="1" t="s">
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B26" s="1">
         <v>27710730</v>
@@ -7027,7 +7021,7 @@
         <v>150</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>26</v>
@@ -7039,35 +7033,41 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="N26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U26" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U26" s="1"/>
       <c r="V26" s="1" t="s">
         <v>166</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>172</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>173</v>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>34</v>
@@ -7216,31 +7216,47 @@
       <c r="I29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
+      <c r="Q29" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R29" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U29" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="V29" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B30" s="1">
         <v>28073088</v>
@@ -7266,40 +7282,24 @@
       <c r="I30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>190</v>
-      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q30" s="1"/>
       <c r="R30" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>191</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U30" s="1"/>
       <c r="V30" s="1" t="s">
         <v>192</v>
       </c>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P40" s="1"/>
       <c r="Q40" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>34</v>
@@ -7878,31 +7878,45 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>257</v>
+      </c>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
+      <c r="Q41" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R41" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B42" s="1">
         <v>31095391</v>
@@ -7922,36 +7936,22 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>259</v>
-      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q42" s="1"/>
       <c r="R42" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -7979,48 +7979,32 @@
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>268</v>
-      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="Q43" s="1"/>
       <c r="R43" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B44" s="1">
         <v>31124688</v>
@@ -8039,23 +8023,39 @@
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
+      <c r="I44" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>270</v>
+      </c>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="Q44" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8081,54 +8081,46 @@
       <c r="F45" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J45" s="1" t="s">
+      <c r="K45" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="M45" s="1"/>
+      <c r="N45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U45" s="1"/>
       <c r="V45" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B46" s="1">
         <v>31217029</v>
@@ -8145,19 +8137,27 @@
       <c r="F46" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
+      <c r="G46" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K46" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="L46" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="L46" s="1" t="s">
+      <c r="M46" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="M46" s="1"/>
       <c r="N46" s="1" t="s">
         <v>27</v>
       </c>
@@ -8166,16 +8166,16 @@
       </c>
       <c r="P46" s="1"/>
       <c r="Q46" s="1" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U46" s="1"/>
       <c r="V46" s="1" t="s">
@@ -8593,7 +8593,7 @@
         <v>326</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="Q54" s="1" t="s">
         <v>33</v>
@@ -8808,39 +8808,55 @@
         <v>343</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
+      <c r="J59" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R59" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S59" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U59" s="1"/>
       <c r="V59" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="1:22">
       <c r="A60" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B60" s="1">
         <v>31445216</v>
@@ -8852,46 +8868,30 @@
         <v>343</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M60" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
       <c r="R60" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
@@ -8912,41 +8912,55 @@
         <v>353</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1" t="s">
         <v>354</v>
       </c>
       <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
+      <c r="J61" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
+      <c r="Q61" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R61" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="62" spans="1:22">
       <c r="A62" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B62" s="1">
         <v>31447154</v>
@@ -8958,46 +8972,32 @@
         <v>353</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
         <v>354</v>
       </c>
       <c r="I62" s="1"/>
-      <c r="J62" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
       <c r="P62" s="1"/>
-      <c r="Q62" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q62" s="1"/>
       <c r="R62" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U62" s="1"/>
       <c r="V62" s="1" t="s">
@@ -9026,31 +9026,43 @@
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
+      <c r="J63" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
+      <c r="M63" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>366</v>
+      </c>
       <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
+      <c r="Q63" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U63" s="1"/>
       <c r="V63" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="64" spans="1:22">
       <c r="A64" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B64" s="1">
         <v>31455868</v>
@@ -9070,34 +9082,22 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-      <c r="J64" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>325</v>
-      </c>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
       <c r="L64" s="1"/>
-      <c r="M64" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>368</v>
-      </c>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
       <c r="P64" s="1"/>
-      <c r="Q64" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q64" s="1"/>
       <c r="R64" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U64" s="1"/>
       <c r="V64" s="1" t="s">
@@ -9214,31 +9214,45 @@
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
+      <c r="J67" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>381</v>
+      </c>
       <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
+      <c r="Q67" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R67" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" spans="1:22">
       <c r="A68" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B68" s="1">
         <v>31475270</v>
@@ -9253,13 +9267,11 @@
         <v>34</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
-      <c r="I68" s="1" t="s">
-        <v>382</v>
-      </c>
+      <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -9279,12 +9291,12 @@
       </c>
       <c r="U68" s="1"/>
       <c r="V68" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="69" spans="1:22">
       <c r="A69" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B69" s="1">
         <v>31475270</v>
@@ -9299,41 +9311,29 @@
         <v>34</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="O69" s="1" t="s">
+      <c r="I69" s="1" t="s">
         <v>387</v>
       </c>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
       <c r="P69" s="1"/>
-      <c r="Q69" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U69" s="1"/>
       <c r="V69" s="1" t="s">
@@ -9352,53 +9352,39 @@
         <v>390</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
-      <c r="J70" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>325</v>
-      </c>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
       <c r="L70" s="1"/>
-      <c r="M70" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71" spans="1:22">
       <c r="A71" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B71" s="1">
         <v>31485048</v>
@@ -9408,30 +9394,44 @@
         <v>390</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
+      <c r="J71" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>325</v>
+      </c>
       <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
+      <c r="M71" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="R71" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S71" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U71" s="1"/>
       <c r="V71" s="1" t="s">
@@ -9530,7 +9530,7 @@
         <v>407</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>34</v>
@@ -9589,7 +9589,7 @@
         <v>414</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q74" s="1" t="s">
         <v>33</v>
@@ -9822,7 +9822,7 @@
         <v>431</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>432</v>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="P82" s="1"/>
       <c r="Q82" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R82" s="1" t="s">
         <v>34</v>
@@ -10194,10 +10194,10 @@
         <v>470</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>469</v>
@@ -10253,7 +10253,7 @@
         <v>217</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>474</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="P87" s="1"/>
       <c r="Q87" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>34</v>
@@ -10308,7 +10308,7 @@
         <v>481</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>482</v>
@@ -10353,7 +10353,7 @@
         <v>34</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -10410,7 +10410,7 @@
         <v>489</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>490</v>
@@ -10518,7 +10518,7 @@
         <v>500</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>501</v>
@@ -10623,7 +10623,7 @@
         <v>58</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>512</v>
@@ -10774,10 +10774,10 @@
         <v>526</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M97" s="1"/>
       <c r="N97" s="1" t="s">
@@ -10832,7 +10832,7 @@
         <v>533</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>31</v>
@@ -11121,7 +11121,7 @@
         <v>58</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M103" s="1" t="s">
         <v>564</v>
@@ -11242,7 +11242,7 @@
         <v>582</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>583</v>
@@ -11514,7 +11514,7 @@
         <v>610</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L110" s="1"/>
       <c r="M110" s="1" t="s">
@@ -11570,7 +11570,7 @@
         <v>616</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L111" s="1"/>
       <c r="M111" s="1"/>
@@ -11584,7 +11584,7 @@
         <v>618</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>26</v>
@@ -11686,10 +11686,10 @@
         <v>631</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>629</v>
@@ -11764,7 +11764,7 @@
         <v>641</v>
       </c>
       <c r="Q114" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R114" s="1" t="s">
         <v>26</v>
@@ -11793,7 +11793,7 @@
         <v>34</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>28</v>
@@ -11817,14 +11817,14 @@
         <v>647</v>
       </c>
       <c r="N115" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="O115" s="1" t="s">
         <v>648</v>
       </c>
       <c r="P115" s="1"/>
       <c r="Q115" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R115" s="1" t="s">
         <v>34</v>
@@ -11914,7 +11914,7 @@
         <v>657</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>98</v>
@@ -11961,7 +11961,7 @@
         <v>34</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>28</v>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P119" s="1"/>
       <c r="Q119" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R119" s="1" t="s">
         <v>34</v>
@@ -12086,7 +12086,7 @@
         <v>672</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>673</v>
@@ -12204,7 +12204,7 @@
         <v>686</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L122" s="1"/>
       <c r="M122" s="1" t="s">
@@ -12366,10 +12366,10 @@
         <v>703</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>704</v>
@@ -12428,7 +12428,7 @@
         <v>710</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>432</v>
@@ -12489,7 +12489,7 @@
         <v>58</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M127" s="1"/>
       <c r="N127" s="1" t="s">
@@ -12644,7 +12644,7 @@
         <v>733</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L130" s="1" t="s">
         <v>734</v>
@@ -12742,10 +12742,10 @@
         <v>742</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M132" s="1" t="s">
         <v>740</v>
@@ -12800,10 +12800,10 @@
         <v>748</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>746</v>
@@ -12903,7 +12903,7 @@
         <v>34</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>28</v>
@@ -12927,7 +12927,7 @@
         <v>758</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="O135" s="1" t="s">
         <v>761</v>
@@ -12980,10 +12980,10 @@
         <v>765</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M136" s="1" t="s">
         <v>764</v>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R136" s="1" t="s">
         <v>34</v>
@@ -13078,7 +13078,7 @@
         <v>773</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L138" s="1" t="s">
         <v>774</v>
@@ -13134,10 +13134,10 @@
         <v>780</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M139" s="1"/>
       <c r="N139" s="1" t="s">
@@ -13221,7 +13221,7 @@
         <v>34</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G141" s="1"/>
       <c r="H141" s="1"/>
@@ -13388,7 +13388,7 @@
         <v>804</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L144" s="1" t="s">
         <v>805</v>
@@ -13647,7 +13647,7 @@
         <v>573</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="M149" s="1"/>
       <c r="N149" s="1" t="s">
@@ -13751,7 +13751,7 @@
         <v>172</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>836</v>
@@ -13916,7 +13916,7 @@
         <v>858</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L154" s="1" t="s">
         <v>859</v>
@@ -13974,10 +13974,10 @@
         <v>865</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>863</v>
@@ -14033,7 +14033,7 @@
         <v>871</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M156" s="1"/>
       <c r="N156" s="1" t="s">
@@ -14186,7 +14186,7 @@
         <v>886</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>814</v>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="P159" s="1"/>
       <c r="Q159" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R159" s="1" t="s">
         <v>34</v>
@@ -14248,7 +14248,7 @@
         <v>893</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="L160" s="1" t="s">
         <v>894</v>
@@ -14324,7 +14324,7 @@
       </c>
       <c r="P161" s="1"/>
       <c r="Q161" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R161" s="1" t="s">
         <v>34</v>
@@ -14355,7 +14355,7 @@
         <v>34</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
@@ -14371,14 +14371,14 @@
       </c>
       <c r="M162" s="1"/>
       <c r="N162" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="O162" s="1" t="s">
         <v>907</v>
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>34</v>
@@ -14424,7 +14424,7 @@
         <v>914</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L163" s="1" t="s">
         <v>179</v>
@@ -14525,7 +14525,7 @@
         <v>924</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M165" s="1"/>
       <c r="N165" s="1" t="s">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="P167" s="1"/>
       <c r="Q167" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R167" s="1" t="s">
         <v>26</v>
@@ -14686,7 +14686,7 @@
         <v>941</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L168" s="1" t="s">
         <v>31</v>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>34</v>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="P170" s="1"/>
       <c r="Q170" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R170" s="1" t="s">
         <v>34</v>
@@ -14868,10 +14868,10 @@
         <v>966</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M171" s="1" t="s">
         <v>967</v>
@@ -14994,7 +14994,7 @@
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>34</v>
@@ -15131,7 +15131,7 @@
         <v>34</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
@@ -15246,10 +15246,10 @@
         <v>1008</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M178" s="1"/>
       <c r="N178" s="1" t="s">
@@ -15309,7 +15309,7 @@
         <v>58</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M179" s="1"/>
       <c r="N179" s="1" t="s">
@@ -15482,7 +15482,7 @@
         <v>1035</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L182" s="1" t="s">
         <v>179</v>
@@ -15594,7 +15594,7 @@
         <v>1046</v>
       </c>
       <c r="K184" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L184" s="1" t="s">
         <v>179</v>
@@ -15637,7 +15637,7 @@
         <v>34</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G185" s="1"/>
       <c r="H185" s="1"/>
@@ -15655,7 +15655,7 @@
         <v>1051</v>
       </c>
       <c r="N185" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="O185" s="1" t="s">
         <v>1052</v>
@@ -15748,10 +15748,10 @@
         <v>1058</v>
       </c>
       <c r="K187" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M187" s="1" t="s">
         <v>1059</v>
@@ -15839,7 +15839,7 @@
         <v>34</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G189" s="1"/>
       <c r="H189" s="1"/>
@@ -15848,16 +15848,16 @@
         <v>1066</v>
       </c>
       <c r="K189" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M189" s="1" t="s">
         <v>1067</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="O189" s="1" t="s">
         <v>1068</v>
@@ -15898,14 +15898,14 @@
         <v>27</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="H190" s="1" t="s">
         <v>1071</v>
       </c>
       <c r="I190" s="1"/>
       <c r="J190" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K190" s="1" t="s">
         <v>58</v>
@@ -16071,7 +16071,7 @@
         <v>1089</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="M193" s="1" t="s">
         <v>1086</v>
@@ -16132,10 +16132,10 @@
         <v>1095</v>
       </c>
       <c r="K194" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="L194" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="L194" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="M194" s="1" t="s">
         <v>1093</v>
@@ -16186,10 +16186,10 @@
         <v>1099</v>
       </c>
       <c r="K195" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M195" s="1" t="s">
         <v>1100</v>
@@ -16251,7 +16251,7 @@
         <v>1107</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M196" s="1" t="s">
         <v>1104</v>
@@ -16306,7 +16306,7 @@
         <v>1113</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L197" s="1" t="s">
         <v>1114</v>
@@ -16481,7 +16481,7 @@
         <v>1134</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>1135</v>
@@ -16934,10 +16934,10 @@
         <v>1187</v>
       </c>
       <c r="K208" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M208" s="1" t="s">
         <v>1185</v>
@@ -17116,7 +17116,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>34</v>
@@ -17223,7 +17223,7 @@
         <v>1217</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M213" s="1" t="s">
         <v>1218</v>
@@ -17236,7 +17236,7 @@
       </c>
       <c r="P213" s="1"/>
       <c r="Q213" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R213" s="1" t="s">
         <v>34</v>
@@ -17283,7 +17283,7 @@
         <v>58</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M214" s="1" t="s">
         <v>1223</v>
@@ -17472,7 +17472,7 @@
         <v>1241</v>
       </c>
       <c r="K218" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L218" s="1" t="s">
         <v>58</v>
@@ -17529,7 +17529,7 @@
         <v>1246</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M219" s="1"/>
       <c r="N219" s="1" t="s">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="P219" s="1"/>
       <c r="Q219" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R219" s="1" t="s">
         <v>34</v>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P223" s="1"/>
       <c r="Q223" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R223" s="1" t="s">
         <v>34</v>
@@ -17827,7 +17827,7 @@
         <v>1273</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M224" s="1" t="s">
         <v>1274</v>
@@ -17887,7 +17887,7 @@
         <v>1281</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M225" s="1" t="s">
         <v>1282</v>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>34</v>
@@ -17945,7 +17945,7 @@
         <v>1246</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M226" s="1" t="s">
         <v>1287</v>
@@ -18005,7 +18005,7 @@
         <v>1246</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M227" s="1" t="s">
         <v>1293</v>
@@ -18078,7 +18078,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>34</v>
@@ -18142,7 +18142,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>34</v>
@@ -18206,7 +18206,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>34</v>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>34</v>
@@ -18434,10 +18434,10 @@
         <v>1342</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M234" s="1" t="s">
         <v>1343</v>
@@ -18450,7 +18450,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>34</v>
@@ -18566,7 +18566,7 @@
         <v>1358</v>
       </c>
       <c r="K236" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L236" s="1" t="s">
         <v>210</v>
@@ -18696,7 +18696,7 @@
         <v>1376</v>
       </c>
       <c r="K238" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L238" s="1" t="s">
         <v>1377</v>
@@ -18712,7 +18712,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>34</v>
@@ -18778,7 +18778,7 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R239" s="1" t="s">
         <v>34</v>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P242" s="1"/>
       <c r="Q242" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R242" s="1" t="s">
         <v>34</v>
@@ -19254,7 +19254,7 @@
         <v>1436</v>
       </c>
       <c r="K247" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L247" s="1" t="s">
         <v>625</v>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="P247" s="1"/>
       <c r="Q247" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R247" s="1" t="s">
         <v>26</v>
@@ -19314,10 +19314,10 @@
         <v>1442</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1441</v>
@@ -19378,10 +19378,10 @@
         <v>1442</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1446</v>
@@ -19456,7 +19456,7 @@
         <v>1456</v>
       </c>
       <c r="Q250" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R250" s="1" t="s">
         <v>34</v>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="P263" s="1"/>
       <c r="Q263" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R263" s="1" t="s">
         <v>34</v>
@@ -20424,7 +20424,7 @@
         <v>1573</v>
       </c>
       <c r="K266" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L266" s="1" t="s">
         <v>98</v>
@@ -20486,7 +20486,7 @@
         <v>1573</v>
       </c>
       <c r="K267" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L267" s="1" t="s">
         <v>98</v>
@@ -20696,7 +20696,7 @@
       </c>
       <c r="P270" s="1"/>
       <c r="Q270" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R270" s="1" t="s">
         <v>34</v>
@@ -20806,7 +20806,7 @@
         <v>1612</v>
       </c>
       <c r="K272" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L272" s="1" t="s">
         <v>179</v>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P272" s="1"/>
       <c r="Q272" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>34</v>
@@ -20866,7 +20866,7 @@
         <v>1612</v>
       </c>
       <c r="K273" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L273" s="1" t="s">
         <v>179</v>
@@ -20882,7 +20882,7 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R273" s="1" t="s">
         <v>34</v>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>34</v>
@@ -21176,7 +21176,7 @@
       </c>
       <c r="P278" s="1"/>
       <c r="Q278" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>34</v>
@@ -21244,7 +21244,7 @@
         <v>1669</v>
       </c>
       <c r="Q279" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R279" s="1" t="s">
         <v>34</v>
